--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>350.45</v>
+        <v>432.45</v>
       </c>
     </row>
     <row r="7">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66.58</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="8">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147.5</v>
+        <v>131.92</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12867</v>
+        <v>12769.42</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>793.17</v>
+        <v>777.59</v>
       </c>
     </row>
     <row r="11">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4174.55</v>
+        <v>4092.55</v>
       </c>
     </row>
     <row r="12">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4174.55</v>
+        <v>4092.55</v>
       </c>
     </row>
     <row r="13">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2087.28</v>
+        <v>2046.28</v>
       </c>
     </row>
     <row r="15">
@@ -1946,10 +1946,14 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Rechnung_RE073.pdf</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5639,22 +5643,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mattha  Wimmler eGbR</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>97.58</v>
+        <v>55.93</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -5665,22 +5669,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>55.93</v>
+        <v>34.85</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -5691,14 +5695,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BOLT (BY STACKBLITZ)</t>
+          <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5706,35 +5710,9 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34.85</v>
+        <v>28.56</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>AUSGABE (Geld raus)</t>
         </is>
@@ -5751,7 +5729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
@@ -6170,26 +6148,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rechnung_RE073.pdf</t>
+          <t>Rechnung_RE0009 (1).pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Matth</t>
+          <t>Benito Ferrise</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RE073</t>
+          <t>RE0009</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>97.58</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6198,7 +6176,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AUSGANG</t>
+          <t>EINGANG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -6210,26 +6188,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rechnung_RE0009 (1).pdf</t>
+          <t>Rechnung Clickfunnel.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Benito Ferrise</t>
+          <t>Digistore24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RE0009</t>
+          <t>I-74568837-de</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>82.98999999999999</v>
+        <v>55.93</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6250,26 +6228,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rechnung Clickfunnel.pdf</t>
+          <t>H_34974301.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Digistore24</t>
+          <t>Hostinger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>I-74568837-de</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>55.93</v>
+        <v>21.41</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6290,21 +6263,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H_34974301.pdf</t>
+          <t>Domain webwokr.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hostinger</t>
+          <t>Wix.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21.41</v>
+        <v>17.79</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -6317,41 +6290,6 @@
         </is>
       </c>
       <c r="H14" t="inlineStr">
-        <is>
-          <t>UNBEKANNT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Domain webwokr.pdf</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Wix.com</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>EINGANG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
         <is>
           <t>UNBEKANNT</t>
         </is>
@@ -6368,7 +6306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6508,61 +6446,61 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97.58</v>
+        <v>93.27</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mattha  Wimmler eGbR</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Frankfurt Event | IBAN: DE63515500350002142891 | BIC: HELADEF1WET</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93.27</v>
+        <v>85.37</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.37</v>
+        <v>83.58</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6583,11 +6521,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.58</v>
+        <v>82.83</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6608,11 +6546,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.83</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6633,11 +6571,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82.79000000000001</v>
+        <v>55.93</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6646,23 +6584,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93</v>
+        <v>52.17</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6671,23 +6609,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52.17</v>
+        <v>35.44</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6708,11 +6646,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35.44</v>
+        <v>34.13</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6733,11 +6671,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.13</v>
+        <v>33.32</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6758,11 +6696,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33.32</v>
+        <v>32.82</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6783,11 +6721,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.82</v>
+        <v>29.54</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6808,11 +6746,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29.54</v>
+        <v>28.56</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6821,73 +6759,73 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.56</v>
+        <v>25.59</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25.59</v>
+        <v>21.33</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.33</v>
+        <v>17.91</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6908,11 +6846,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.91</v>
+        <v>17.73</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6921,23 +6859,23 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17.73</v>
+        <v>17.12</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6950,31 +6888,6 @@
         </is>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
@@ -7385,28 +7298,28 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>69.73999999999999</v>
+        <v>151.74</v>
       </c>
       <c r="E10" t="n">
         <v>442.86</v>
       </c>
       <c r="F10" t="n">
-        <v>-69.73999999999999</v>
+        <v>-151.74</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>13.25</v>
+        <v>28.83</v>
       </c>
       <c r="I10" t="n">
-        <v>28.92</v>
+        <v>13.34</v>
       </c>
       <c r="J10" t="n">
-        <v>-13.25</v>
+        <v>-28.83</v>
       </c>
       <c r="K10" t="n">
-        <v>359.87</v>
+        <v>262.29</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
@@ -7539,28 +7452,28 @@
         <v>10924.46</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>350.45</v>
+        <v>432.45</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7744.32</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4174.55</v>
+        <v>4092.55</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>859.75</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>66.58</v>
+        <v>82.16</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>147.5</v>
+        <v>131.92</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>793.17</v>
+        <v>777.59</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>12867</v>
+        <v>12769.42</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>36</v>
@@ -12798,7 +12711,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -16283,10 +16196,14 @@
       <c r="I70" t="b">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Rechnung_RE073.pdf</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -453,192 +453,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kennzahl</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Wert (EUR)</t>
-        </is>
-      </c>
+          <t>HAUPTKENNZAHLEN (Netto-Basis, nur aus Belegen mit expliziter Netto-Angabe)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Umsatz brutto</t>
+          <t>Umsatz netto</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10924.46</v>
+        <v>4525</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Umsatz netto</t>
+          <t>USt vereinnahmt</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4525</v>
+        <v>859.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>USt vereinnahmt</t>
+          <t>Ausgaben netto</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>859.75</v>
+        <v>432.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ausgaben brutto</t>
+          <t>Vorsteuer abziehbar</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7744.32</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ausgaben netto</t>
+          <t>USt-Zahllast (vereinnahmt - abziehbar)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>432.45</v>
+        <v>777.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vorsteuer abziehbar</t>
+          <t>Gewinn netto (Umsatz netto - Ausgaben netto)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.16</v>
+        <v>4092.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vorsteuer gefaehrdet (geschaetzt, mangels Beleg nicht abziehbar)</t>
+          <t>Gewerbeertrag Basis (= Gewinn netto, RECHNERISCH)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>131.92</v>
+        <v>4092.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brutto ohne Netto-/USt-Aufteilung</t>
+          <t>Gewerbeertrag nach Freibetrag 24.500 EUR (RECHNERISCH)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12769.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>USt-Zahllast (vereinnahmt - abziehbar)</t>
+          <t>Gewinnanteil je Gesellschafter, netto (50/50)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>777.59</v>
+        <v>2046.28</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Gewinn vorlaeufig (Umsatz netto - Ausgaben netto)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4092.55</v>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gewerbeertrag Basis (= Gewinn vorlaeufig, RECHNERISCH)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4092.55</v>
-      </c>
+          <t>ZUR EINORDNUNG (Brutto, vollstaendig, aber ohne Netto-/USt-Aufschluesselung)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gewerbeertrag nach Freibetrag 24.500 EUR (RECHNERISCH)</t>
+          <t>Umsatz brutto (alle Zahlungen)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>10924.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gewinnanteil je Gesellschafter (50/50)</t>
+          <t>Ausgaben brutto (alle Zahlungen)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2046.28</v>
+        <v>7744.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anzahl Pruefaelle (Transaktionsebene)</t>
+          <t>Brutto ohne Netto-/USt-Aufteilung (kein/unvollstaendiger Beleg - fehlt oben im Netto-Gewinn)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36</v>
+        <v>12769.42</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vorsteuer gefaehrdet (geschaetzt, mangels Beleg nicht abziehbar)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>131.92</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HINWEIS:</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>RECHNERISCH, ohne Hinzurechnungen/Kuerzungen (§§8,9 GewStG), ohne Abschreibungen, ohne Abgrenzungen -&gt; Steuerberater konsultieren.</t>
-        </is>
+          <t>Anzahl Pruefaelle (Transaktionsebene)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HINWEIS:</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Schritt 3 (Gmail) ist ausgefallen: 'Request had insufficient authentication scopes' - OAuth-Berechtigung fuer Gmail fehlt. Keine E-Mail-Belege in dieser Auswertung enthalten.</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -648,7 +632,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Schritt 1 (Lexoffice) hat keine Bank-Transaktions-API - Transaktionsgrundlage ist der vom Nutzer bereitgestellte Finom-Kontoauszug (Finom_statement_21072026.pdf, 29.10.2024-21.07.2026), auf 2025 gefiltert.</t>
+          <t>HAUPTKENNZAHL ist 'gewinn_netto' (Umsatz netto - Ausgaben netto), NUR aus Zahlungen mit einem Beleg, der eine explizite Netto-/USt-Angabe traegt - kein Wert wird geschaetzt oder aus dem Bruttobetrag zurueckgerechnet. Zahlungen ohne diese Angabe fehlen in dieser Kennzahl (siehe 'brutto_ohne_aufteilung' und die Statistik-Tabs) und muessen erst per Beleg geklaert werden, bevor sie den Netto-Gewinn veraendern. 'ergebnis_brutto' ist zur Einordnung danebengestellt. Kein echter steuerlicher Gewinn (keine Abschreibungen/Abgrenzungen/Hinzurechnungen) -&gt; Steuerberater konsultieren.</t>
         </is>
       </c>
     </row>
@@ -660,7 +644,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USt-Voranmeldungen 2025 werden vom Nutzer selbst geprueft, kein Abgleich in diesem Lauf.</t>
+          <t>Schritt 3 (Gmail) ist ausgefallen: 'Request had insufficient authentication scopes' - OAuth-Berechtigung fuer Gmail fehlt. Keine E-Mail-Belege in dieser Auswertung enthalten.</t>
         </is>
       </c>
     </row>
@@ -671,6 +655,30 @@
         </is>
       </c>
       <c r="B21" t="inlineStr">
+        <is>
+          <t>Schritt 1 (Lexoffice) hat keine Bank-Transaktions-API - Transaktionsgrundlage ist der vom Nutzer bereitgestellte Finom-Kontoauszug (Finom_statement_21072026.pdf, 29.10.2024-21.07.2026), auf 2025 gefiltert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HINWEIS:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>USt-Voranmeldungen 2025 werden vom Nutzer selbst geprueft, kein Abgleich in diesem Lauf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HINWEIS:</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Diese Auswertung ist eine Datengrundlage, KEINE Steuerberatung.</t>
         </is>
@@ -6912,7 +6920,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -6949,7 +6957,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Gewinn</t>
+          <t>Gewinn netto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>432.45</v>
+        <v>785.45</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.16</v>
+        <v>127.76</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>777.59</v>
+        <v>731.99</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4092.55</v>
+        <v>3739.55</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4092.55</v>
+        <v>3739.55</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2046.28</v>
+        <v>1869.78</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12769.42</v>
+        <v>12361.99</v>
       </c>
     </row>
     <row r="16">
@@ -7002,13 +7002,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>9.949999999999999</v>
+        <v>34.95</v>
       </c>
       <c r="E2" t="n">
         <v>47.31</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.949999999999999</v>
+        <v>-34.95</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -7023,7 +7023,7 @@
         <v>-1.89</v>
       </c>
       <c r="K2" t="n">
-        <v>35.47</v>
+        <v>5.72</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -7040,13 +7040,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>19.9</v>
+        <v>44.9</v>
       </c>
       <c r="E3" t="n">
         <v>53.43</v>
       </c>
       <c r="F3" t="n">
-        <v>-19.9</v>
+        <v>-44.9</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7061,7 +7061,7 @@
         <v>-3.78</v>
       </c>
       <c r="K3" t="n">
-        <v>29.75</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -7078,13 +7078,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>19.9</v>
+        <v>44.9</v>
       </c>
       <c r="E4" t="n">
         <v>89.05</v>
       </c>
       <c r="F4" t="n">
-        <v>-19.9</v>
+        <v>-44.9</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
         <v>-3.78</v>
       </c>
       <c r="K4" t="n">
-        <v>65.37</v>
+        <v>35.62</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -7154,13 +7154,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>19.9</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>186.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.9</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -7175,7 +7175,7 @@
         <v>-3.78</v>
       </c>
       <c r="K6" t="n">
-        <v>162.5</v>
+        <v>103</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -7230,13 +7230,13 @@
         <v>25.59</v>
       </c>
       <c r="D8" t="n">
-        <v>19.9</v>
+        <v>44.9</v>
       </c>
       <c r="E8" t="n">
         <v>169.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-19.9</v>
+        <v>-44.9</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>-3.78</v>
       </c>
       <c r="K8" t="n">
-        <v>171.69</v>
+        <v>141.94</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -7268,28 +7268,28 @@
         <v>212.27</v>
       </c>
       <c r="D9" t="n">
-        <v>21.9</v>
+        <v>60.9</v>
       </c>
       <c r="E9" t="n">
         <v>487.83</v>
       </c>
       <c r="F9" t="n">
-        <v>78.09999999999999</v>
+        <v>39.1</v>
       </c>
       <c r="G9" t="n">
         <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>4.16</v>
+        <v>49.76</v>
       </c>
       <c r="I9" t="n">
         <v>17.26</v>
       </c>
       <c r="J9" t="n">
-        <v>14.84</v>
+        <v>-30.76</v>
       </c>
       <c r="K9" t="n">
-        <v>555.04</v>
+        <v>514.77</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -7306,13 +7306,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>151.74</v>
+        <v>215.74</v>
       </c>
       <c r="E10" t="n">
         <v>442.86</v>
       </c>
       <c r="F10" t="n">
-        <v>-151.74</v>
+        <v>-215.74</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>-28.83</v>
       </c>
       <c r="K10" t="n">
-        <v>262.29</v>
+        <v>192.63</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
@@ -7344,13 +7344,13 @@
         <v>660.85</v>
       </c>
       <c r="D11" t="n">
-        <v>68.90000000000001</v>
+        <v>118.9</v>
       </c>
       <c r="E11" t="n">
         <v>268.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-68.90000000000001</v>
+        <v>-118.9</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -7365,7 +7365,7 @@
         <v>-13.09</v>
       </c>
       <c r="K11" t="n">
-        <v>847.61</v>
+        <v>788.11</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -7382,13 +7382,13 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>51.04</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>759.75</v>
       </c>
       <c r="F12" t="n">
-        <v>373.96</v>
+        <v>348.96</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
@@ -7403,7 +7403,7 @@
         <v>71.05</v>
       </c>
       <c r="K12" t="n">
-        <v>699.01</v>
+        <v>669.26</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -7420,13 +7420,13 @@
         <v>9520</v>
       </c>
       <c r="D13" t="n">
-        <v>9.52</v>
+        <v>34.52</v>
       </c>
       <c r="E13" t="n">
         <v>4991.82</v>
       </c>
       <c r="F13" t="n">
-        <v>3990.48</v>
+        <v>3965.48</v>
       </c>
       <c r="G13" t="n">
         <v>760</v>
@@ -7441,7 +7441,7 @@
         <v>758.1900000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>9740.49</v>
+        <v>9710.74</v>
       </c>
       <c r="L13" t="n">
         <v>18</v>
@@ -7460,28 +7460,28 @@
         <v>10924.46</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>432.45</v>
+        <v>785.45</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7744.32</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>4092.55</v>
+        <v>3739.55</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>859.75</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>82.16</v>
+        <v>127.76</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>131.92</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>777.59</v>
+        <v>731.99</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>12769.42</v>
+        <v>12361.99</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>36</v>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>785.45</v>
+        <v>1566.25</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3739.55</v>
+        <v>2958.75</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3739.55</v>
+        <v>2958.75</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1869.78</v>
+        <v>1479.38</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12361.99</v>
+        <v>11606.63</v>
       </c>
     </row>
     <row r="16">
@@ -7078,13 +7078,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>44.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>89.05</v>
       </c>
       <c r="F4" t="n">
-        <v>-44.9</v>
+        <v>-81.90000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
         <v>-3.78</v>
       </c>
       <c r="K4" t="n">
-        <v>35.62</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -7192,13 +7192,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>19.9</v>
+        <v>39.9</v>
       </c>
       <c r="E7" t="n">
         <v>143.58</v>
       </c>
       <c r="F7" t="n">
-        <v>-19.9</v>
+        <v>-39.9</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>-3.78</v>
       </c>
       <c r="K7" t="n">
-        <v>119.9</v>
+        <v>102.49</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -7268,13 +7268,13 @@
         <v>212.27</v>
       </c>
       <c r="D9" t="n">
-        <v>60.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E9" t="n">
         <v>487.83</v>
       </c>
       <c r="F9" t="n">
-        <v>39.1</v>
+        <v>19.1</v>
       </c>
       <c r="G9" t="n">
         <v>19</v>
@@ -7289,7 +7289,7 @@
         <v>-30.76</v>
       </c>
       <c r="K9" t="n">
-        <v>514.77</v>
+        <v>497.59</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -7306,13 +7306,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>215.74</v>
+        <v>235.74</v>
       </c>
       <c r="E10" t="n">
         <v>442.86</v>
       </c>
       <c r="F10" t="n">
-        <v>-215.74</v>
+        <v>-235.74</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>-28.83</v>
       </c>
       <c r="K10" t="n">
-        <v>192.63</v>
+        <v>175.56</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
@@ -7382,13 +7382,13 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>76.04000000000001</v>
+        <v>623.04</v>
       </c>
       <c r="E12" t="n">
         <v>759.75</v>
       </c>
       <c r="F12" t="n">
-        <v>348.96</v>
+        <v>-198.04</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
@@ -7403,7 +7403,7 @@
         <v>71.05</v>
       </c>
       <c r="K12" t="n">
-        <v>669.26</v>
+        <v>134.94</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -7420,13 +7420,13 @@
         <v>9520</v>
       </c>
       <c r="D13" t="n">
-        <v>34.52</v>
+        <v>171.32</v>
       </c>
       <c r="E13" t="n">
         <v>4991.82</v>
       </c>
       <c r="F13" t="n">
-        <v>3965.48</v>
+        <v>3828.68</v>
       </c>
       <c r="G13" t="n">
         <v>760</v>
@@ -7441,7 +7441,7 @@
         <v>758.1900000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>9710.74</v>
+        <v>9576.98</v>
       </c>
       <c r="L13" t="n">
         <v>18</v>
@@ -7460,13 +7460,13 @@
         <v>10924.46</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>785.45</v>
+        <v>1566.25</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7744.32</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3739.55</v>
+        <v>2958.75</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>859.75</v>
@@ -7481,7 +7481,7 @@
         <v>731.99</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>12361.99</v>
+        <v>11606.63</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>36</v>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1566.25</v>
+        <v>1673.45</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>127.76</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>731.99</v>
+        <v>713.52</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2958.75</v>
+        <v>2851.55</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2958.75</v>
+        <v>2851.55</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1479.38</v>
+        <v>1425.78</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11606.63</v>
+        <v>11480.96</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>131.92</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="17">
@@ -704,8 +704,8 @@
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1086,10 +1086,14 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Drive:dabdf808-8706-4d9c-8111-ac218a331f15.html (Rechnung Nr. 3OJ3-0004 PNL Fintech)</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3195,7 @@
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
@@ -3782,10 +3786,14 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5625,22 +5633,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PNL Fintech B.V.</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>115.67</v>
+        <v>55.93</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -5651,22 +5659,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55.93</v>
+        <v>34.85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -5677,14 +5685,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BOLT (BY STACKBLITZ)</t>
+          <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5692,35 +5700,9 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>34.85</v>
+        <v>28.56</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>AUSGABE (Geld raus)</t>
         </is>
@@ -6314,7 +6296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6429,61 +6411,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115.67</v>
+        <v>93.27</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PNL Fintech B.V.</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Annual fee for Basic plan (incl. VAT). | Subscription period: 29 Nov, 2025 - 28 Nov, | 2026</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93.27</v>
+        <v>85.37</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85.37</v>
+        <v>83.58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6504,11 +6486,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.58</v>
+        <v>82.83</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6529,11 +6511,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82.83</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6554,11 +6536,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.79000000000001</v>
+        <v>55.93</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6567,23 +6549,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55.93</v>
+        <v>52.17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6592,23 +6574,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52.17</v>
+        <v>35.44</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6629,11 +6611,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.44</v>
+        <v>34.13</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6654,11 +6636,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.13</v>
+        <v>33.32</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6679,11 +6661,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33.32</v>
+        <v>32.82</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6704,11 +6686,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.82</v>
+        <v>29.54</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6729,11 +6711,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.54</v>
+        <v>28.56</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6742,73 +6724,73 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>PADDLE.NET* N8N CLOUD1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.56</v>
+        <v>25.59</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25.59</v>
+        <v>21.33</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.33</v>
+        <v>17.91</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6829,11 +6811,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.91</v>
+        <v>17.73</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6842,23 +6824,23 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.73</v>
+        <v>17.12</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6871,31 +6853,6 @@
         </is>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>BOLT (BY STACKBLITZ)</t>
         </is>
@@ -7154,13 +7111,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>69.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>186.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-69.90000000000001</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -7175,7 +7132,7 @@
         <v>-3.78</v>
       </c>
       <c r="K6" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -7230,13 +7187,13 @@
         <v>25.59</v>
       </c>
       <c r="D8" t="n">
-        <v>44.9</v>
+        <v>49.9</v>
       </c>
       <c r="E8" t="n">
         <v>169.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-44.9</v>
+        <v>-49.9</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -7251,7 +7208,7 @@
         <v>-3.78</v>
       </c>
       <c r="K8" t="n">
-        <v>141.94</v>
+        <v>136.94</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -7382,28 +7339,28 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>623.04</v>
+        <v>720.24</v>
       </c>
       <c r="E12" t="n">
         <v>759.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-198.04</v>
+        <v>-295.24</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
       </c>
       <c r="H12" t="n">
-        <v>9.699999999999999</v>
+        <v>28.17</v>
       </c>
       <c r="I12" t="n">
-        <v>18.47</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>71.05</v>
+        <v>52.58</v>
       </c>
       <c r="K12" t="n">
-        <v>134.94</v>
+        <v>19.27</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -7460,28 +7417,28 @@
         <v>10924.46</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1566.25</v>
+        <v>1673.45</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7744.32</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2958.75</v>
+        <v>2851.55</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>859.75</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>127.76</v>
+        <v>146.23</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>131.92</v>
+        <v>113.45</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>731.99</v>
+        <v>713.52</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>11606.63</v>
+        <v>11480.96</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>36</v>
@@ -10558,7 +10515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10879,20 +10836,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4.32</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PNL Fintech B.V.</t>
+          <t>FINDYLEAD.COM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FINOM-a78c9dc8bf2894fe</t>
+          <t>FINOM-0934e4ba1f2bf7b5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10904,30 +10861,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PNL Fintech B.V.</t>
+          <t>Invoice number CXFCCFMI-0003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FINOM-fee739b336e336b6</t>
+          <t>Invoice-CXFCCFMI-0003.pdf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19% (unterstellt)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10939,20 +10896,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.32</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FINDYLEAD.COM</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FINOM-0934e4ba1f2bf7b5</t>
+          <t>FINOM-24bba19c4344d8c2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10969,83 +10926,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.48</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Invoice number CXFCCFMI-0003</t>
+          <t>Digistore24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Invoice-CXFCCFMI-0003.pdf</t>
+          <t>Rechnung_TJC9SRX6_73763127-de.pdf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>FINOM-24bba19c4344d8c2</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>19% (unterstellt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Digistore24</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rechnung_TJC9SRX6_73763127-de.pdf</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -12672,7 +12569,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -12719,7 +12616,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -12734,7 +12631,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
@@ -14550,10 +14447,14 @@
       <c r="I36" t="b">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Drive:05b869a0-4824-4fb2-b89f-cdb651e1dad6.html (Rechnung Nr. 3OJ3-0003 PNL Fintech)</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -15375,10 +15276,14 @@
       <c r="I53" t="b">
         <v>0</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Drive:dabdf808-8706-4d9c-8111-ac218a331f15.html (Rechnung Nr. 3OJ3-0004 PNL Fintech)</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -18257,10 +18162,14 @@
       <c r="I111" t="b">
         <v>0</v>
       </c>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Drive:876cdb25-f3f5-4c8e-87b7-9c44fbc3f49e.html (Rechnung Nr. 3OJ3-0005 PNL Fintech)</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -21176,8 +21085,8 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -21603,10 +21512,14 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Drive:05b869a0-4824-4fb2-b89f-cdb651e1dad6.html (Rechnung Nr. 3OJ3-0003 PNL Fintech)</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AKZEPTIERT_BAGATELLE</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4525</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>859.75</v>
+        <v>940.5</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1673.45</v>
+        <v>2302.2</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>146.23</v>
+        <v>150.79</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>713.52</v>
+        <v>789.71</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2851.55</v>
+        <v>2647.8</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2851.55</v>
+        <v>2647.8</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1425.78</v>
+        <v>1323.9</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11480.96</v>
+        <v>10341.9</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>113.45</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="17">
@@ -821,10 +821,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0010.pdf</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -902,10 +911,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Paddle n8n Cloud Beleg 10-07-2025.md</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Nur per Gmail gefunden (Paddle-Beleg 73531154-143210765), kein PDF-Anhang, als Textbeleg dokumentiert. Betrag/MwSt exakt aus Beleg uebernommen.</t>
         </is>
       </c>
     </row>
@@ -1275,10 +1293,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0014.pdf</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -1809,10 +1836,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Funnelcockpit_2.pdf</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KORRIGIERT 2026-07-22: Beleg war faelschlich 09-29 UND 10-28 zugeordnet (Datumsextraktion hatte Leistungsdatum statt Rechnungsdatum uebernommen). Rechnung datiert 27.08.2025 -&gt; gehoert zur 08-28-Zahlung.</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2151,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0016.pdf</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -2516,14 +2561,15 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Funnelcockpit_2.pdf</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BELEGT</t>
+          <t>BELEG_FEHLT</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Vormals faelschlich Funnelcockpit_2.pdf zugeordnet (siehe Korrektur 2026-07-22) - Beleg wurde 08-28 zugewiesen. Echte September-Rechnung noch nicht gefunden.</t>
         </is>
       </c>
     </row>
@@ -2705,10 +2751,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0018.pdf</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2796,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0019.pdf</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -2777,10 +2841,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Anzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -3015,10 +3088,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Restzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3171,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Funnelcockpit_2.pdf</t>
+          <t>Rechnung Clickfunnel.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aus Drive nachgeladen 2026-07-22 (war lokal nicht vorhanden). Korrigiert Fehlzuordnung von Funnelcockpit_2.pdf.</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5227,7 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -5314,12 +5401,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NEIN</t>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RE250006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Anzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -5374,12 +5476,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NEIN</t>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RE250006</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Restzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -5509,10 +5626,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -5555,154 +5672,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>591.23</v>
+        <v>273.96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>505.75</v>
+        <v>55.93</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>273.96</v>
+        <v>21.33</v>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>UMSATZ (Geld rein)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>AUSGABE (Geld raus)</t>
         </is>
@@ -6296,13 +6335,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -6336,11 +6375,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>275</v>
+        <v>155.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6349,23 +6388,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>230.75</v>
+        <v>93.27</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6374,48 +6413,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>155.1</v>
+        <v>55.93</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93.27</v>
+        <v>25.59</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6429,18 +6468,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2024 | 93,27 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85.37</v>
+        <v>21.33</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6455,406 +6494,6 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>83.58</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>82.83</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>82.79000000000001</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>35.44</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>34.13</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>33.32</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>29.54</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PADDLE.NET* N8N CLOUD1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>25.59</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>UMSATZ (Geld rein)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>17.91</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>17.73</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>BOLT (BY STACKBLITZ)</t>
         </is>
       </c>
     </row>
@@ -7073,13 +6712,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>19.9</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>103.98</v>
       </c>
       <c r="F5" t="n">
-        <v>-19.9</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7088,13 +6727,13 @@
         <v>3.78</v>
       </c>
       <c r="I5" t="n">
-        <v>10.77</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-3.78</v>
       </c>
       <c r="K5" t="n">
-        <v>80.3</v>
+        <v>12.85</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -7111,13 +6750,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>74.90000000000001</v>
+        <v>172.9</v>
       </c>
       <c r="E6" t="n">
         <v>186.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-74.90000000000001</v>
+        <v>-172.9</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -7126,13 +6765,13 @@
         <v>3.78</v>
       </c>
       <c r="I6" t="n">
-        <v>15.65</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>-3.78</v>
       </c>
       <c r="K6" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -7149,13 +6788,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>39.9</v>
+        <v>142.39</v>
       </c>
       <c r="E7" t="n">
         <v>143.58</v>
       </c>
       <c r="F7" t="n">
-        <v>-39.9</v>
+        <v>-142.39</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -7164,13 +6803,13 @@
         <v>3.78</v>
       </c>
       <c r="I7" t="n">
-        <v>16.36</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>-3.78</v>
       </c>
       <c r="K7" t="n">
-        <v>102.49</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -7187,28 +6826,28 @@
         <v>25.59</v>
       </c>
       <c r="D8" t="n">
-        <v>49.9</v>
+        <v>156.69</v>
       </c>
       <c r="E8" t="n">
         <v>169.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-49.9</v>
+        <v>-156.69</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.78</v>
+        <v>8.34</v>
       </c>
       <c r="I8" t="n">
-        <v>17.78</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.78</v>
+        <v>-8.34</v>
       </c>
       <c r="K8" t="n">
-        <v>136.94</v>
+        <v>25.59</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -7225,28 +6864,28 @@
         <v>212.27</v>
       </c>
       <c r="D9" t="n">
-        <v>80.90000000000001</v>
+        <v>180.07</v>
       </c>
       <c r="E9" t="n">
         <v>487.83</v>
       </c>
       <c r="F9" t="n">
-        <v>19.1</v>
+        <v>-80.06999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>49.76</v>
+        <v>58.69</v>
       </c>
       <c r="I9" t="n">
-        <v>17.26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-30.76</v>
+        <v>-39.69</v>
       </c>
       <c r="K9" t="n">
-        <v>497.59</v>
+        <v>389.49</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -7263,28 +6902,28 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>235.74</v>
+        <v>272.32</v>
       </c>
       <c r="E10" t="n">
         <v>442.86</v>
       </c>
       <c r="F10" t="n">
-        <v>-235.74</v>
+        <v>-272.32</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>28.83</v>
+        <v>19.9</v>
       </c>
       <c r="I10" t="n">
-        <v>13.34</v>
+        <v>8.93</v>
       </c>
       <c r="J10" t="n">
-        <v>-28.83</v>
+        <v>-19.9</v>
       </c>
       <c r="K10" t="n">
-        <v>175.56</v>
+        <v>147.91</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
@@ -7295,34 +6934,34 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="C11" t="n">
         <v>660.85</v>
       </c>
       <c r="D11" t="n">
-        <v>118.9</v>
+        <v>237.17</v>
       </c>
       <c r="E11" t="n">
         <v>268.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-118.9</v>
+        <v>187.83</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>80.75</v>
       </c>
       <c r="H11" t="n">
         <v>13.09</v>
       </c>
       <c r="I11" t="n">
-        <v>18.88</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.09</v>
+        <v>67.66</v>
       </c>
       <c r="K11" t="n">
-        <v>788.11</v>
+        <v>164.09</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -7411,34 +7050,34 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4525</v>
+        <v>4950</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>10924.46</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1673.45</v>
+        <v>2302.2</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7744.32</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2851.55</v>
+        <v>2647.8</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>859.75</v>
+        <v>940.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>146.23</v>
+        <v>150.79</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>113.45</v>
+        <v>12.34</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>713.52</v>
+        <v>789.71</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>11480.96</v>
+        <v>10341.9</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>36</v>
@@ -7455,13 +7094,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -7582,7 +7221,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7595,7 +7234,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Instantly 06 25.pdf</t>
+          <t>Instantly 07 25.pdf</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7617,7 +7256,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -7630,7 +7269,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Instantly 07 25.pdf</t>
+          <t>Receipt-2172-3201.pdf</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7640,32 +7279,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>97</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0010.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-c20ea1051ef014f4)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7675,32 +7314,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Fremdwaehrungs-Beleg gefunden (97.0 USD), Bankbuchung in EUR (84.32) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2172-3201.pdf)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>97</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Benito Ferrise</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0016.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-b6c9180f60ec69e7)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7710,32 +7349,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 82.99 am 2025-09-11 bei mehreren Buchungen: Benito Ferrise (EINGANG), Mohamed Amin Douioui (AUSGANG)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>97</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Mohamed Amin Douioui</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0019.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-bd6b0b450552e893)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7745,7 +7384,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 82.99 am 2025-09-11 bei mehreren Buchungen: Benito Ferrise (EINGANG), Mohamed Amin Douioui (AUSGANG)</t>
         </is>
       </c>
     </row>
@@ -7755,22 +7394,17 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
       <c r="C9" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>FA / SF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Receipt-2172-3201.pdf</t>
+          <t>Rechnung_RE26-0054.pdf</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7780,32 +7414,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.31999999999999</v>
+        <v>59.42</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-c20ea1051ef014f4)</t>
+          <t>Instantly 08 25.pdf</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7815,32 +7449,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (97.0 USD), Bankbuchung in EUR (84.32) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2172-3201.pdf)</t>
+          <t>Fremdwaehrung vermutet: USD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>82.98999999999999</v>
+        <v>46.41</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Benito Ferrise</t>
+          <t>Apify Technologies</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-b6c9180f60ec69e7)</t>
+          <t>Apify_Invoice_202508060773.pdf</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7850,32 +7484,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 82.99 am 2025-09-11 bei mehreren Buchungen: Benito Ferrise (EINGANG), Mohamed Amin Douioui (AUSGANG)</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>82.98999999999999</v>
+        <v>46.41</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mohamed Amin Douioui</t>
+          <t>Apify Technologies</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-bd6b0b450552e893)</t>
+          <t>Apify_Invoice_202509060156.pdf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7885,27 +7519,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 82.99 am 2025-09-11 bei mehreren Buchungen: Benito Ferrise (EINGANG), Mohamed Amin Douioui (AUSGANG)</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>40.27</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FA / SF</t>
+          <t>APIFY* SUBSCRIPTION</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rechnung_RE26-0054.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-7d7d463ef8cf4269)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7915,32 +7554,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rechnungsdatum nicht eindeutig extrahierbar</t>
+          <t>Fremdwaehrungs-Beleg gefunden (46.41 USD), Bankbuchung in EUR (40.27) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Apify_Invoice_202508060773.pdf)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>59.42</v>
+        <v>39.91</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>APIFY* INV#20250906015</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Instantly 08 25.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-475e932a333a0a51)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7950,7 +7589,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Fremdwaehrungs-Beleg gefunden (46.41 USD), Bankbuchung in EUR (39.91) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Apify_Invoice_202509060156.pdf)</t>
         </is>
       </c>
     </row>
@@ -7962,11 +7601,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>59.42</v>
+        <v>37</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7975,7 +7614,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0014.pdf</t>
+          <t>Instantly 03 25.pdf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -7985,32 +7624,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>46.41</v>
+        <v>35.62</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apify Technologies</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Apify_Invoice_202508060773.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-d3f6b2877412abff)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8020,32 +7659,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Fremdwaehrungs-Beleg gefunden (37.0 USD), Bankbuchung in EUR (35.62) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 03 25.pdf)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>46.41</v>
+        <v>29.75</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apify Technologies</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Apify_Invoice_202509060156.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-06064dc6caeffc3e)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -8055,7 +7694,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -8067,20 +7706,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40.27</v>
+        <v>29.75</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>APIFY* SUBSCRIPTION</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-7d7d463ef8cf4269)</t>
+          <t>Finom-Kontoauszug (FINOM-107d120bc6c97c90)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8090,32 +7729,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (46.41 USD), Bankbuchung in EUR (40.27) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Apify_Invoice_202508060773.pdf)</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>29.75</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0018.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-7a5509a20459c553)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -8125,7 +7764,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -8137,20 +7776,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>39.91</v>
+        <v>29.75</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>APIFY* INV#20250906015</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-475e932a333a0a51)</t>
+          <t>Finom-Kontoauszug (FINOM-fc23049c19eef787)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -8160,32 +7799,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (46.41 USD), Bankbuchung in EUR (39.91) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Apify_Invoice_202509060156.pdf)</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>29.75</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Triathlon Transfer GmbH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Instantly 03 25.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-573950e7ce0a8d96)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -8195,32 +7834,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>29.75</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Instantly 04 25.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-8b0621350826004d)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8230,32 +7869,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37</v>
+        <v>29.75</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Instantly 050 25.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-dd03f910c4ab1f1c)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8265,7 +7904,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -8277,20 +7916,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35.62</v>
+        <v>29.75</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-d3f6b2877412abff)</t>
+          <t>Finom-Kontoauszug (FINOM-16223eeb17f02926)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -8300,32 +7939,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (37.0 USD), Bankbuchung in EUR (35.62) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 03 25.pdf)</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>29.75</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Instantly 041 25.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-d362ba2859a500aa)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8335,32 +7974,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>32.87</v>
+        <v>29.75</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Instantly 05 25.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-22c0361defcb2229)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8370,7 +8009,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8021,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -8395,7 +8034,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-06064dc6caeffc3e)</t>
+          <t>Finom-Kontoauszug (FINOM-30e897bc56d3efb8)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8412,12 +8051,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2025-02-28</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -8425,12 +8059,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Triathlon Transfer</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-107d120bc6c97c90)</t>
+          <t>Triathlon Miete.pdf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8440,32 +8074,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Kein Rechnungsdatum extrahierbar, Zuordnung ueber Betrag+Partner</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29.75</v>
+        <v>28.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-7a5509a20459c553)</t>
+          <t>5615032135.pdf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8475,7 +8104,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
@@ -8487,20 +8116,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.75</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Mohamed Amin Douioui</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-fc23049c19eef787)</t>
+          <t>Finom-Kontoauszug (FINOM-1a2f1f13d2cc058e)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8510,7 +8139,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 25.0 am 2025-04-11 bei mehreren Buchungen: Mohamed Amin Douioui (AUSGANG), Mohamed Amin Douioui (AUSGANG)</t>
         </is>
       </c>
     </row>
@@ -8522,20 +8151,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>29.75</v>
+        <v>25</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Triathlon Transfer GmbH</t>
+          <t>Mohamed Amin Douioui</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-573950e7ce0a8d96)</t>
+          <t>Finom-Kontoauszug (FINOM-0d2d2718b19a2f29)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -8545,7 +8174,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 25.0 am 2025-04-11 bei mehreren Buchungen: Mohamed Amin Douioui (AUSGANG), Mohamed Amin Douioui (AUSGANG)</t>
         </is>
       </c>
     </row>
@@ -8557,20 +8186,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.75</v>
+        <v>24</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>GAMMA.APP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-8b0621350826004d)</t>
+          <t>Finom-Kontoauszug (FINOM-1d00c1c63a0e30d1)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -8580,32 +8209,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'GAMMA.APP' vs. Beleg-Partner 'Invoice number GMM5S7YE-0001' (Invoice-GMM5S7YE-0001.pdf)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.75</v>
+        <v>24</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Invoice number GMM5S7YE-0001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-dd03f910c4ab1f1c)</t>
+          <t>Invoice-GMM5S7YE-0001.pdf</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -8615,32 +8244,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29.75</v>
+        <v>21.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-16223eeb17f02926)</t>
+          <t>Receipt-2265-8647.pdf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -8650,7 +8279,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
@@ -8662,20 +8291,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>29.75</v>
+        <v>21.41</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>HOSTINGER* HOSTINGER.D</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-d362ba2859a500aa)</t>
+          <t>Finom-Kontoauszug (FINOM-f119331e6bae481c)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -8685,32 +8314,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Mehrere Beleg-Kandidaten mit passender Rechnungsnummer/Partner+Zeitfenster: H_33541164.pdf (Beleg 6649835b); H_34974301.pdf (Beleg aa369ac3)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>29.75</v>
+        <v>20</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-22c0361defcb2229)</t>
+          <t>Instantly 061 25.pdf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -8720,32 +8349,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>29.75</v>
+        <v>20</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-30e897bc56d3efb8)</t>
+          <t>Invoice-BCE54405-0015.pdf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8755,7 +8384,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Beleg ohne Rechnungsdatum, Partner passt, Betrag passt - bitte Datum pruefen (Triathlon Miete.pdf)</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
@@ -8765,17 +8394,22 @@
           <t>Beleg</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
       <c r="C38" t="n">
-        <v>29.75</v>
+        <v>20</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Triathlon Transfer</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Triathlon Miete.pdf</t>
+          <t>Invoice-BCE54405-0017.pdf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -8785,27 +8419,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kein Rechnungsdatum extrahierbar, Zuordnung ueber Betrag+Partner</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>28.1</v>
+        <v>18.76</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5615032135.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-dda344ea0a0755e4)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -8815,7 +8454,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rechnungsdatum nicht eindeutig extrahierbar</t>
+          <t>Fremdwaehrungs-Beleg gefunden (21.8 USD), Bankbuchung in EUR (18.76) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2265-8647.pdf)</t>
         </is>
       </c>
     </row>
@@ -8827,20 +8466,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>17.41</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mohamed Amin Douioui</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-1a2f1f13d2cc058e)</t>
+          <t>Finom-Kontoauszug (FINOM-823c1e5f5d8e821b)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8850,7 +8489,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 25.0 am 2025-04-11 bei mehreren Buchungen: Mohamed Amin Douioui (AUSGANG), Mohamed Amin Douioui (AUSGANG)</t>
+          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.41) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 061 25.pdf)</t>
         </is>
       </c>
     </row>
@@ -8862,20 +8501,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>17.18</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mohamed Amin Douioui</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-0d2d2718b19a2f29)</t>
+          <t>Finom-Kontoauszug (FINOM-88cc4b8a8c6557c9)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8885,7 +8524,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 25.0 am 2025-04-11 bei mehreren Buchungen: Mohamed Amin Douioui (AUSGANG), Mohamed Amin Douioui (AUSGANG)</t>
+          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.18) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0015.pdf)</t>
         </is>
       </c>
     </row>
@@ -8897,20 +8536,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>24</v>
+        <v>17.07</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GAMMA.APP</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-1d00c1c63a0e30d1)</t>
+          <t>Finom-Kontoauszug (FINOM-2be6110d96082159)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8920,32 +8559,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'GAMMA.APP' vs. Beleg-Partner 'Invoice number GMM5S7YE-0001' (Invoice-GMM5S7YE-0001.pdf)</t>
+          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.07) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0017.pdf)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Invoice number GMM5S7YE-0001</t>
+          <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Invoice-GMM5S7YE-0001.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-c0cfd1dc5c8f6e79)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8955,7 +8594,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QUFFB9ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf)</t>
         </is>
       </c>
     </row>
@@ -8967,20 +8606,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>21.8</v>
+        <v>14</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Receipt-2265-8647.pdf</t>
+          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8990,7 +8629,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
@@ -9002,20 +8641,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21.41</v>
+        <v>12</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HOSTINGER* HOSTINGER.D</t>
+          <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-f119331e6bae481c)</t>
+          <t>Finom-Kontoauszug (FINOM-e82ca75e4b3f4578)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9025,7 +8664,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mehrere Beleg-Kandidaten mit passender Rechnungsnummer/Partner+Zeitfenster: H_33541164.pdf (Beleg 6649835b); H_34974301.pdf (Beleg aa369ac3)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BNNY6A5MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf)</t>
         </is>
       </c>
     </row>
@@ -9037,20 +8676,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Instantly 051 25.pdf</t>
+          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9060,32 +8699,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Instantly 061 25.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-b28ec8e545dd43f3)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9095,7 +8734,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *4Q76L9RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf)</t>
         </is>
       </c>
     </row>
@@ -9107,20 +8746,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0015.pdf</t>
+          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9130,32 +8769,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0017.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-86f39f49ff54efcc)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9165,7 +8804,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *C3GR9A9MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf)</t>
         </is>
       </c>
     </row>
@@ -9177,20 +8816,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Rechnungsnummer LRDKYW8R-0002</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Invoice-LRDKYW8R-0002.pdf</t>
+          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9200,7 +8839,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
@@ -9212,20 +8851,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>18.76</v>
+        <v>9</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-dda344ea0a0755e4)</t>
+          <t>Finom-Kontoauszug (FINOM-71d1133d3242ef87)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9235,32 +8874,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (21.8 USD), Bankbuchung in EUR (18.76) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2265-8647.pdf)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QHNPD9DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>17.41</v>
+        <v>9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-823c1e5f5d8e821b)</t>
+          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9270,7 +8909,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.41) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 061 25.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
@@ -9282,20 +8921,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17.18</v>
+        <v>8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>FACEBK *WSY378HLU2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-88cc4b8a8c6557c9)</t>
+          <t>Finom-Kontoauszug (FINOM-5bb24d5e7aac7dae)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -9305,32 +8944,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.18) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0015.pdf)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *WSY378HLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17.07</v>
+        <v>8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-2be6110d96082159)</t>
+          <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -9340,7 +8979,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.07) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0017.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
@@ -9352,20 +8991,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FACEBK *QUFFB9ZLU2</t>
+          <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-c0cfd1dc5c8f6e79)</t>
+          <t>Finom-Kontoauszug (FINOM-f355060b825f4014)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9375,7 +9014,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QUFFB9ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BMHJC8VLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf)</t>
         </is>
       </c>
     </row>
@@ -9387,11 +9026,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9400,7 +9039,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
+          <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9422,20 +9061,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FACEBK *BNNY6A5MU2</t>
+          <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-e82ca75e4b3f4578)</t>
+          <t>Finom-Kontoauszug (FINOM-df923a4f5a3743c2)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -9445,7 +9084,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BNNY6A5MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *YHJ6S8ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf)</t>
         </is>
       </c>
     </row>
@@ -9457,11 +9096,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9470,7 +9109,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
+          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -9492,20 +9131,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FACEBK *4Q76L9RLU2</t>
+          <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-b28ec8e545dd43f3)</t>
+          <t>Finom-Kontoauszug (FINOM-d9984f5bceeea21f)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9515,7 +9154,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *4Q76L9RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *XFZ769DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf)</t>
         </is>
       </c>
     </row>
@@ -9527,11 +9166,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9540,7 +9179,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
+          <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -9562,20 +9201,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>4.02</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FACEBK *C3GR9A9MU2</t>
+          <t>KAFFEEROSTEREI COMAME</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-86f39f49ff54efcc)</t>
+          <t>Finom-Kontoauszug (FINOM-8e80729325a162a5)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -9585,32 +9224,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *C3GR9A9MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf)</t>
+          <t>Gegenpartei/Verwendungszweck nicht eindeutig zuordenbar: 'KAFFEEROSTEREI COMAME' / 'KAFFEEROSTEREI COMAME'</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-46b66624a2376b78)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -9620,32 +9259,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *JFQQ29DMU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FACEBK *QHNPD9DLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-71d1133d3242ef87)</t>
+          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -9655,32 +9294,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QHNPD9DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-f916f37b2a3745ba)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -9690,32 +9329,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *HLN339MLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FACEBK *WSY378HLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-5bb24d5e7aac7dae)</t>
+          <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -9725,32 +9364,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *WSY378HLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-6729b513d41029a4)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -9760,32 +9399,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *UFNK69RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FACEBK *BMHJC8VLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-f355060b825f4014)</t>
+          <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -9795,7 +9434,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BMHJC8VLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
@@ -9805,22 +9444,14 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>7</v>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>AMERICAN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
+          <t>2026-07-13-image001.png</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9830,32 +9461,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>6</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>FACEBK *YHJ6S8ZLU2</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-df923a4f5a3743c2)</t>
+          <t>01fae0.png</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9865,7 +9483,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *YHJ6S8ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf)</t>
+          <t>Kein extrahierbarer Text (auch nach OCR-Versuch leer) - vermutlich kein lesbarer Beleg; Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9493,14 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>6</v>
-      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Kostenkalkulation</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
+          <t>Kostenkalkulation.pdf</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9900,32 +9510,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar; Fremdwaehrung vermutet: USD</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>5</v>
+          <t>Beleg</t>
+        </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FACEBK *XFZ769DLU2</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-d9984f5bceeea21f)</t>
+          <t>Leistungsübersicht der Business Platinum Card.pdf</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9935,7 +9537,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *XFZ769DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf)</t>
+          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
@@ -9945,22 +9547,14 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>5</v>
-      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>AMERICAN</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
+          <t>image001.png</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -9970,32 +9564,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAFFEEROSTEREI COMAME</t>
+          <t>Apify Technologies</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-8e80729325a162a5)</t>
+          <t>Apify_Invoice_202510060569.pdf</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -10005,32 +9599,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gegenpartei/Verwendungszweck nicht eindeutig zuordenbar: 'KAFFEEROSTEREI COMAME' / 'KAFFEEROSTEREI COMAME'</t>
+          <t>Fremdwaehrung vermutet: USD</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>4</v>
+          <t>Beleg</t>
+        </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FACEBK *JFQQ29DMU2</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-46b66624a2376b78)</t>
+          <t>Finanzamt Bescheid.pdf</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -10040,7 +9626,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *JFQQ29DMU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf)</t>
+          <t>Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
@@ -10050,22 +9636,9 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>4</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
+          <t>Finom_statement_01042026.pdf</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -10075,32 +9648,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>3</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>FACEBK *HLN339MLU2</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-f916f37b2a3745ba)</t>
+          <t>Finom_statement_30122025 (1).pdf</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -10110,7 +9670,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *HLN339MLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf)</t>
+          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
         </is>
       </c>
     </row>
@@ -10120,22 +9680,9 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>3</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
+          <t>Finom_statement_31122025.pdf</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -10145,32 +9692,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>2</v>
+          <t>Beleg</t>
+        </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FACEBK *UFNK69RLU2</t>
+          <t>© American Express®</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-6729b513d41029a4)</t>
+          <t>Mitgliedschaftsbedingungen.pdf</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -10179,326 +9718,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *UFNK69RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>2</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>AMERICAN</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-07-13-image001.png</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>01fae0.png</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Kein extrahierbarer Text (auch nach OCR-Versuch leer) - vermutlich kein lesbarer Beleg; Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Kostenkalkulation</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Kostenkalkulation.pdf</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar; Fremdwaehrung vermutet: USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Leistungsübersicht der Business Platinum Card.pdf</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>AMERICAN</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>image001.png</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Apify Technologies</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Apify_Invoice_202510060569.pdf</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Fremdwaehrung vermutet: USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Finanzamt</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Finanzamt Bescheid.pdf</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Finom_statement_01042026.pdf</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Finom_statement_30122025 (1).pdf</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Finom_statement_31122025.pdf</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>© American Express®</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Mitgliedschaftsbedingungen.pdf</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
@@ -12569,7 +11788,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -12616,7 +11835,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -12631,7 +11850,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
@@ -13612,10 +12831,19 @@
       <c r="I19" t="b">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Instantly 04 25.pdf</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -13659,10 +12887,19 @@
       <c r="I20" t="b">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Instantly 041 25.pdf</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -14105,10 +13342,19 @@
       <c r="I29" t="b">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Instantly 050 25.pdf</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -14203,10 +13449,19 @@
       <c r="I31" t="b">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Instantly 051 25.pdf</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -14250,10 +13505,19 @@
       <c r="I32" t="b">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Instantly 05 25.pdf</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -14498,10 +13762,19 @@
       <c r="I37" t="b">
         <v>1</v>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Nur per Gmail gefunden (Stripe-Zahlungsbeleg Nr. 2514-9086), PDF-Anhang nicht abrufbar, als Textbeleg dokumentiert. Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -14639,10 +13912,19 @@
       <c r="I40" t="b">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Instantly 06 25.pdf</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -14840,10 +14122,19 @@
       <c r="I44" t="b">
         <v>1</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Invoice-LRDKYW8R-0002.pdf</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -14934,10 +14225,19 @@
       <c r="I46" t="b">
         <v>1</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0010.pdf</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -15037,10 +14337,19 @@
       <c r="I48" t="b">
         <v>0</v>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Paddle n8n Cloud Beleg 10-07-2025.md</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Nur per Gmail gefunden (Paddle-Beleg 73531154-143210765), kein PDF-Anhang, als Textbeleg dokumentiert. Betrag/MwSt exakt aus Beleg uebernommen.</t>
         </is>
       </c>
     </row>
@@ -15374,10 +14683,19 @@
       <c r="I55" t="b">
         <v>1</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0014.pdf</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -16062,10 +15380,19 @@
       <c r="I69" t="b">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Funnelcockpit_2.pdf</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>KORRIGIERT 2026-07-22: Beleg war faelschlich 09-29 UND 10-28 zugeordnet (Datumsextraktion hatte Leistungsdatum statt Rechnungsdatum uebernommen). Rechnung datiert 27.08.2025 -&gt; gehoert zur 08-28-Zahlung.</t>
         </is>
       </c>
     </row>
@@ -16310,10 +15637,19 @@
       <c r="I74" t="b">
         <v>1</v>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0016.pdf</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -16821,14 +16157,15 @@
       <c r="I84" t="b">
         <v>0</v>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Funnelcockpit_2.pdf</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>BELEGT</t>
+          <t>BELEG_FEHLT</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Vormals faelschlich Funnelcockpit_2.pdf zugeordnet (siehe Korrektur 2026-07-22) - Beleg wurde 08-28 zugewiesen. Echte September-Rechnung noch nicht gefunden.</t>
         </is>
       </c>
     </row>
@@ -16919,10 +16256,19 @@
       <c r="I86" t="b">
         <v>0</v>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0018.pdf</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -16966,10 +16312,19 @@
       <c r="I87" t="b">
         <v>1</v>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Invoice-BCE54405-0019.pdf</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -17013,10 +16368,19 @@
       <c r="I88" t="b">
         <v>0</v>
       </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Anzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -17317,10 +16681,19 @@
       <c r="I94" t="b">
         <v>0</v>
       </c>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Restzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -17413,12 +16786,17 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Funnelcockpit_2.pdf</t>
+          <t>Rechnung Clickfunnel.pdf</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Aus Drive nachgeladen 2026-07-22 (war lokal nicht vorhanden). Korrigiert Fehlzuordnung von Funnelcockpit_2.pdf.</t>
         </is>
       </c>
     </row>
@@ -20598,7 +19976,7 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
@@ -20751,10 +20129,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Instantly 04 25.pdf</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -20787,10 +20174,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Instantly 041 25.pdf</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -21086,7 +20482,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -21247,10 +20643,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Instantly 050 25.pdf</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -21323,10 +20728,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Instantly 051 25.pdf</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -21359,10 +20773,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Instantly 05 25.pdf</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -21552,10 +20975,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bolt StackBlitz Beleg 05-29-2025.md</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nur per Gmail gefunden (Stripe-Zahlungsbeleg Nr. 2514-9086), PDF-Anhang nicht abrufbar, als Textbeleg dokumentiert. Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -21620,8 +21052,8 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -21773,10 +21205,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Instantly 06 25.pdf</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>
@@ -21930,10 +21371,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Invoice-LRDKYW8R-0002.pdf</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Fremdwaehrungsbeleg (USD-Rechnung), EUR-Betrag aus Bank-Kartenumrechnung uebernommen. Manuell recherchiert/verifiziert 2026-07-22.</t>
         </is>
       </c>
     </row>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2302.2</v>
+        <v>2236.68</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150.79</v>
+        <v>148.6</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>789.71</v>
+        <v>791.9</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2647.8</v>
+        <v>2713.32</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2647.8</v>
+        <v>2713.32</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1323.9</v>
+        <v>1356.66</v>
       </c>
     </row>
     <row r="11">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10924.46</v>
+        <v>5890.5</v>
       </c>
     </row>
     <row r="14">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7744.32</v>
+        <v>2859.06</v>
       </c>
     </row>
     <row r="15">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10341.9</v>
+        <v>490.39</v>
       </c>
     </row>
     <row r="16">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -6601,7 +6601,7 @@
         <v>34.95</v>
       </c>
       <c r="E2" t="n">
-        <v>47.31</v>
+        <v>41.59</v>
       </c>
       <c r="F2" t="n">
         <v>-34.95</v>
@@ -6619,7 +6619,7 @@
         <v>-1.89</v>
       </c>
       <c r="K2" t="n">
-        <v>5.72</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -6750,13 +6750,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>172.9</v>
+        <v>167.9</v>
       </c>
       <c r="E6" t="n">
-        <v>186.18</v>
+        <v>181.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-172.9</v>
+        <v>-167.9</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6823,16 +6823,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>25.59</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>156.69</v>
+        <v>151.69</v>
       </c>
       <c r="E8" t="n">
-        <v>169.78</v>
+        <v>164.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-156.69</v>
+        <v>-151.69</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>-8.34</v>
       </c>
       <c r="K8" t="n">
-        <v>25.59</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -6861,13 +6861,13 @@
         <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>212.27</v>
+        <v>119</v>
       </c>
       <c r="D9" t="n">
         <v>180.07</v>
       </c>
       <c r="E9" t="n">
-        <v>487.83</v>
+        <v>477.21</v>
       </c>
       <c r="F9" t="n">
         <v>-80.06999999999999</v>
@@ -6885,7 +6885,7 @@
         <v>-39.69</v>
       </c>
       <c r="K9" t="n">
-        <v>389.49</v>
+        <v>285.6</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -6902,28 +6902,28 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>272.32</v>
+        <v>271.48</v>
       </c>
       <c r="E10" t="n">
-        <v>442.86</v>
+        <v>432.87</v>
       </c>
       <c r="F10" t="n">
-        <v>-272.32</v>
+        <v>-271.48</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>19.9</v>
+        <v>19.74</v>
       </c>
       <c r="I10" t="n">
         <v>8.93</v>
       </c>
       <c r="J10" t="n">
-        <v>-19.9</v>
+        <v>-19.74</v>
       </c>
       <c r="K10" t="n">
-        <v>147.91</v>
+        <v>138.92</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
@@ -6937,13 +6937,13 @@
         <v>425</v>
       </c>
       <c r="C11" t="n">
-        <v>660.85</v>
+        <v>505.75</v>
       </c>
       <c r="D11" t="n">
         <v>237.17</v>
       </c>
       <c r="E11" t="n">
-        <v>268.75</v>
+        <v>259.76</v>
       </c>
       <c r="F11" t="n">
         <v>187.83</v>
@@ -6961,7 +6961,7 @@
         <v>67.66</v>
       </c>
       <c r="K11" t="n">
-        <v>164.09</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -6978,28 +6978,28 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>720.24</v>
+        <v>719.08</v>
       </c>
       <c r="E12" t="n">
-        <v>759.75</v>
+        <v>749.38</v>
       </c>
       <c r="F12" t="n">
-        <v>-295.24</v>
+        <v>-294.08</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
       </c>
       <c r="H12" t="n">
-        <v>28.17</v>
+        <v>27.95</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>52.58</v>
+        <v>52.8</v>
       </c>
       <c r="K12" t="n">
-        <v>19.27</v>
+        <v>10.28</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -7013,34 +7013,34 @@
         <v>4000</v>
       </c>
       <c r="C13" t="n">
-        <v>9520</v>
+        <v>4760</v>
       </c>
       <c r="D13" t="n">
-        <v>171.32</v>
+        <v>117.8</v>
       </c>
       <c r="E13" t="n">
-        <v>4991.82</v>
+        <v>162.25</v>
       </c>
       <c r="F13" t="n">
-        <v>3828.68</v>
+        <v>3882.2</v>
       </c>
       <c r="G13" t="n">
         <v>760</v>
       </c>
       <c r="H13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>3.41</v>
       </c>
       <c r="J13" t="n">
-        <v>758.1900000000001</v>
+        <v>760</v>
       </c>
       <c r="K13" t="n">
-        <v>9576.98</v>
+        <v>42.74</v>
       </c>
       <c r="L13" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -7053,34 +7053,34 @@
         <v>4950</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>10924.46</v>
+        <v>5890.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2302.2</v>
+        <v>2236.68</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>7744.32</v>
+        <v>2859.06</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2647.8</v>
+        <v>2713.32</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>150.79</v>
+        <v>148.6</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>12.34</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>789.71</v>
+        <v>791.9</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>10341.9</v>
+        <v>490.39</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2236.68</v>
+        <v>2319.59</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>148.6</v>
+        <v>164.36</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>791.9</v>
+        <v>776.14</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2713.32</v>
+        <v>2630.41</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2713.32</v>
+        <v>2630.41</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1356.66</v>
+        <v>1315.2</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>490.39</v>
+        <v>391.72</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2561,15 +2561,14 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rechnung_TJC9SRX6_I-74230203-de.pdf</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Vormals faelschlich Funnelcockpit_2.pdf zugeordnet (siehe Korrektur 2026-07-22) - Beleg wurde 08-28 zugewiesen. Echte September-Rechnung noch nicht gefunden.</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -4669,10 +4668,19 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>(kein Originalbeleg - akzeptiert)</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>AKZEPTIERT_BAGATELLE</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Per Nutzerentscheidung 2026-07-22 akzeptiert: keine Rechnung auffindbar trotz mehrfacher Recherche (Drive komplett, Gmail). Netto geschaetzt mit 19% USt aus Bankbetrag.</t>
         </is>
       </c>
     </row>
@@ -4921,15 +4929,14 @@
           <t>GESCHAEFTLICH</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>H_34974301.pdf</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Mehrere Beleg-Kandidaten mit passender Rechnungsnummer/Partner+Zeitfenster: H_33541164.pdf (Beleg 6649835b); H_34974301.pdf (Beleg aa369ac3)</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5634,7 +5641,7 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5692,58 +5699,6 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>UMSATZ (Geld rein)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
@@ -6257,21 +6212,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H_34974301.pdf</t>
+          <t>Domain webwokr.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hostinger</t>
+          <t>Wix.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21.41</v>
+        <v>17.79</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6284,41 +6239,6 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
-        <is>
-          <t>UNBEKANNT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Domain webwokr.pdf</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Wix.com</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>17.79</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EINGANG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
         <is>
           <t>UNBEKANNT</t>
         </is>
@@ -6335,12 +6255,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
@@ -6425,75 +6345,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.93</v>
+        <v>25.59</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>25.59</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>UMSATZ (Geld rein)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>ERSTATT.040/163/12016 UMS.ST 2VJ.25 | 25,59 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AUSGABE (Geld raus)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>INSTANTLY</t>
         </is>
       </c>
     </row>
@@ -6902,28 +6772,28 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>271.48</v>
+        <v>318.48</v>
       </c>
       <c r="E10" t="n">
         <v>432.87</v>
       </c>
       <c r="F10" t="n">
-        <v>-271.48</v>
+        <v>-318.48</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>19.74</v>
+        <v>28.67</v>
       </c>
       <c r="I10" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-19.74</v>
+        <v>-28.67</v>
       </c>
       <c r="K10" t="n">
-        <v>138.92</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
@@ -7016,31 +6886,31 @@
         <v>4760</v>
       </c>
       <c r="D13" t="n">
-        <v>117.8</v>
+        <v>153.71</v>
       </c>
       <c r="E13" t="n">
         <v>162.25</v>
       </c>
       <c r="F13" t="n">
-        <v>3882.2</v>
+        <v>3846.29</v>
       </c>
       <c r="G13" t="n">
         <v>760</v>
       </c>
       <c r="H13" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.41</v>
-      </c>
       <c r="J13" t="n">
-        <v>760</v>
+        <v>753.17</v>
       </c>
       <c r="K13" t="n">
-        <v>42.74</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -7056,31 +6926,31 @@
         <v>5890.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2236.68</v>
+        <v>2319.59</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>2859.06</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2713.32</v>
+        <v>2630.41</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>148.6</v>
+        <v>164.36</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>12.34</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>791.9</v>
+        <v>776.14</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>490.39</v>
+        <v>391.72</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7094,7 +6964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8286,25 +8156,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>21.41</v>
+        <v>20</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HOSTINGER* HOSTINGER.D</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-f119331e6bae481c)</t>
+          <t>Instantly 061 25.pdf</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -8314,7 +8184,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mehrere Beleg-Kandidaten mit passender Rechnungsnummer/Partner+Zeitfenster: H_33541164.pdf (Beleg 6649835b); H_34974301.pdf (Beleg aa369ac3)</t>
+          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8196,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -8339,7 +8209,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Instantly 061 25.pdf</t>
+          <t>Invoice-BCE54405-0015.pdf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -8361,7 +8231,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -8374,7 +8244,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0015.pdf</t>
+          <t>Invoice-BCE54405-0017.pdf</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8391,25 +8261,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>20</v>
+        <v>18.76</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Invoice-BCE54405-0017.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-dda344ea0a0755e4)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -8419,7 +8289,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fremdwaehrungsbeleg, Bankbetrag weicht wegen Kartenumrechnung ab - manuell pruefen</t>
+          <t>Fremdwaehrungs-Beleg gefunden (21.8 USD), Bankbuchung in EUR (18.76) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2265-8647.pdf)</t>
         </is>
       </c>
     </row>
@@ -8431,11 +8301,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>18.76</v>
+        <v>17.41</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8444,7 +8314,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-dda344ea0a0755e4)</t>
+          <t>Finom-Kontoauszug (FINOM-823c1e5f5d8e821b)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -8454,7 +8324,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (21.8 USD), Bankbuchung in EUR (18.76) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Receipt-2265-8647.pdf)</t>
+          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.41) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 061 25.pdf)</t>
         </is>
       </c>
     </row>
@@ -8466,11 +8336,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.41</v>
+        <v>17.18</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -8479,7 +8349,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-823c1e5f5d8e821b)</t>
+          <t>Finom-Kontoauszug (FINOM-88cc4b8a8c6557c9)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8489,7 +8359,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.41) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Instantly 061 25.pdf)</t>
+          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.18) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0015.pdf)</t>
         </is>
       </c>
     </row>
@@ -8501,11 +8371,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>17.18</v>
+        <v>17.07</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -8514,7 +8384,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-88cc4b8a8c6557c9)</t>
+          <t>Finom-Kontoauszug (FINOM-2be6110d96082159)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8524,7 +8394,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.18) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0015.pdf)</t>
+          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.07) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0017.pdf)</t>
         </is>
       </c>
     </row>
@@ -8536,20 +8406,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.07</v>
+        <v>14</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INSTANTLY</t>
+          <t>FACEBK *QUFFB9ZLU2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-2be6110d96082159)</t>
+          <t>Finom-Kontoauszug (FINOM-c0cfd1dc5c8f6e79)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8559,19 +8429,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fremdwaehrungs-Beleg gefunden (20.0 USD), Bankbuchung in EUR (17.07) nach Kartenumrechnung - Betrag NICHT automatisch umgerechnet, bitte Wechselkurs/Zuordnung manuell pruefen (Invoice-BCE54405-0017.pdf)</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QUFFB9ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -8579,12 +8449,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FACEBK *QUFFB9ZLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-c0cfd1dc5c8f6e79)</t>
+          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8594,14 +8464,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QUFFB9ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8610,16 +8480,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *BNNY6A5MU2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-12-18T20-09 Transaktion 25556351544054971-25365991733090951.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-e82ca75e4b3f4578)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8629,19 +8499,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BNNY6A5MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -8649,12 +8519,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FACEBK *BNNY6A5MU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-e82ca75e4b3f4578)</t>
+          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8664,14 +8534,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BNNY6A5MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8680,16 +8550,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *4Q76L9RLU2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-12-17T13-22 Transaktion 25323714033985385-25323714057318716.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-b28ec8e545dd43f3)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8699,19 +8569,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *4Q76L9RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -8719,12 +8589,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FACEBK *4Q76L9RLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-b28ec8e545dd43f3)</t>
+          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8734,32 +8604,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *4Q76L9RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *C3GR9A9MU2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-12-16T09-14 Transaktion 25533610619662397-25501444542879004.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-86f39f49ff54efcc)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -8769,14 +8639,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *C3GR9A9MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8789,12 +8659,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FACEBK *C3GR9A9MU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-86f39f49ff54efcc)</t>
+          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -8804,14 +8674,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *C3GR9A9MU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8820,16 +8690,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *QHNPD9DLU2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-12-15T00-11 Transaktion 25416472061376255-25521729800850479.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-71d1133d3242ef87)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -8839,19 +8709,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QHNPD9DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -8859,12 +8729,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FACEBK *QHNPD9DLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-71d1133d3242ef87)</t>
+          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -8874,14 +8744,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *QHNPD9DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8890,16 +8760,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *WSY378HLU2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-12-14T13-11 Transaktion 25414279194928869-25297331939956928.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-5bb24d5e7aac7dae)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -8909,19 +8779,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *WSY378HLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -8929,12 +8799,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FACEBK *WSY378HLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-5bb24d5e7aac7dae)</t>
+          <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -8944,14 +8814,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *WSY378HLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8960,16 +8830,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *BMHJC8VLU2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-12-13T12-47 Transaktion 25476762878680504-25421830257507097.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-f355060b825f4014)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -8979,19 +8849,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BMHJC8VLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -8999,12 +8869,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FACEBK *BMHJC8VLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-f355060b825f4014)</t>
+          <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9014,14 +8884,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *BMHJC8VLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9030,16 +8900,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *YHJ6S8ZLU2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-12T07-30 Transaktion 25277831071907015-25392863410403787.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-df923a4f5a3743c2)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9049,14 +8919,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *YHJ6S8ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9069,12 +8939,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FACEBK *YHJ6S8ZLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-df923a4f5a3743c2)</t>
+          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -9084,14 +8954,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *YHJ6S8ZLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9100,16 +8970,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *XFZ769DLU2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-12-12T00-14 Transaktion 25355385920818200-25408368092186647.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-d9984f5bceeea21f)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -9119,19 +8989,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *XFZ769DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -9139,12 +9009,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FACEBK *XFZ769DLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-d9984f5bceeea21f)</t>
+          <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9154,32 +9024,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *XFZ769DLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>4.02</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>KAFFEEROSTEREI COMAME</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-12-11T13-26 Transaktion 25491332630556863-25386252381064890.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-8e80729325a162a5)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -9189,7 +9059,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Gegenpartei/Verwendungszweck nicht eindeutig zuordenbar: 'KAFFEEROSTEREI COMAME' / 'KAFFEEROSTEREI COMAME'</t>
         </is>
       </c>
     </row>
@@ -9201,20 +9071,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KAFFEEROSTEREI COMAME</t>
+          <t>FACEBK *JFQQ29DMU2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-8e80729325a162a5)</t>
+          <t>Finom-Kontoauszug (FINOM-46b66624a2376b78)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -9224,19 +9094,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gegenpartei/Verwendungszweck nicht eindeutig zuordenbar: 'KAFFEEROSTEREI COMAME' / 'KAFFEEROSTEREI COMAME'</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *JFQQ29DMU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -9244,12 +9114,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FACEBK *JFQQ29DMU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-46b66624a2376b78)</t>
+          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -9259,32 +9129,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *JFQQ29DMU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *HLN339MLU2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-12-11T11-05 Transaktion 25458338170522975-25385334284490033.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-f916f37b2a3745ba)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -9294,19 +9164,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *HLN339MLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -9314,12 +9184,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FACEBK *HLN339MLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-f916f37b2a3745ba)</t>
+          <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -9329,14 +9199,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *HLN339MLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9345,16 +9215,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>FACEBK *UFNK69RLU2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-12-11T09-46 Transaktion 25386529371037185-25349826548040804.pdf</t>
+          <t>Finom-Kontoauszug (FINOM-6729b513d41029a4)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -9364,19 +9234,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *UFNK69RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Transaktion</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -9384,12 +9254,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FACEBK *UFNK69RLU2</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Finom-Kontoauszug (FINOM-6729b513d41029a4)</t>
+          <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -9399,7 +9269,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag+Zeitfenster, Partner nicht eindeutig: Transaktion 'FACEBK *UFNK69RLU2' vs. Beleg-Partner 'Meta Platforms' (2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf)</t>
+          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
         </is>
       </c>
     </row>
@@ -9409,22 +9279,14 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>2</v>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>AMERICAN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-12-10T22-33 Transaktion 25398762293147227-25382391428117646.pdf</t>
+          <t>2026-07-13-image001.png</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -9434,7 +9296,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Zuordnung nur ueber Betrag, Partner nicht eindeutig bestaetigt</t>
+          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
@@ -9444,14 +9306,9 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>AMERICAN</t>
-        </is>
-      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-13-image001.png</t>
+          <t>01fae0.png</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9461,7 +9318,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
+          <t>Kein extrahierbarer Text (auch nach OCR-Versuch leer) - vermutlich kein lesbarer Beleg; Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar</t>
         </is>
       </c>
     </row>
@@ -9471,9 +9328,14 @@
           <t>Beleg</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Kostenkalkulation</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>01fae0.png</t>
+          <t>Kostenkalkulation.pdf</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9483,7 +9345,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kein extrahierbarer Text (auch nach OCR-Versuch leer) - vermutlich kein lesbarer Beleg; Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar</t>
+          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar; Fremdwaehrung vermutet: USD</t>
         </is>
       </c>
     </row>
@@ -9495,12 +9357,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kostenkalkulation</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kostenkalkulation.pdf</t>
+          <t>Leistungsübersicht der Business Platinum Card.pdf</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9510,7 +9372,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar; Fremdwaehrung vermutet: USD</t>
+          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9384,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>AMERICAN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Leistungsübersicht der Business Platinum Card.pdf</t>
+          <t>image001.png</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9547,14 +9409,22 @@
           <t>Beleg</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AMERICAN</t>
+          <t>Apify Technologies</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>image001.png</t>
+          <t>Apify_Invoice_202510060569.pdf</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -9564,7 +9434,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
+          <t>Fremdwaehrung vermutet: USD</t>
         </is>
       </c>
     </row>
@@ -9574,22 +9444,14 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apify Technologies</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Apify_Invoice_202510060569.pdf</t>
+          <t>Finanzamt Bescheid.pdf</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -9599,7 +9461,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fremdwaehrung vermutet: USD</t>
+          <t>Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
       </c>
     </row>
@@ -9609,14 +9471,9 @@
           <t>Beleg</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Finanzamt</t>
-        </is>
-      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Finanzamt Bescheid.pdf</t>
+          <t>Finom_statement_01042026.pdf</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -9626,7 +9483,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
+          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9495,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Finom_statement_01042026.pdf</t>
+          <t>Finom_statement_30122025 (1).pdf</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -9660,7 +9517,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Finom_statement_30122025 (1).pdf</t>
+          <t>Finom_statement_31122025.pdf</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9680,9 +9537,14 @@
           <t>Beleg</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>© American Express®</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Finom_statement_31122025.pdf</t>
+          <t>Mitgliedschaftsbedingungen.pdf</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9691,33 +9553,6 @@
         </is>
       </c>
       <c r="G77" t="inlineStr">
-        <is>
-          <t>Kontoauszug-Teilexport (mehrere Transaktionen), kein Einzelbeleg - Inhalt bereits ueber den vollstaendigen Finom-Kontoauszug (Schritt 1, Transaktionsliste) erfasst. Nur zur Doku behalten, nicht separat zuordnen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Beleg</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>© American Express®</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Mitgliedschaftsbedingungen.pdf</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>Richtung (AUSGANG/EINGANG) nicht eindeutig bestimmbar - EIGENE_FIRMA weder als Aussteller noch als Empfaenger klar erkennbar; Bruttobetrag nicht eindeutig extrahierbar; Rechnungsdatum nicht eindeutig extrahierbar</t>
         </is>
@@ -9734,7 +9569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9785,20 +9620,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12.85</v>
+        <v>21.33</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ZOHO-ZOHO CORP</t>
+          <t>INSTANTLY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FINOM-d0d29a90ec518cd9</t>
+          <t>FINOM-ac0930c40ca669af</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9810,25 +9645,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Transaktion</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
+          <t>Beleg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.28</v>
+        <v>21.33</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FINOM-537cc943fa0b335d</t>
+          <t>(kein Originalbeleg - akzeptiert)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -9845,20 +9675,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.99</v>
+        <v>12.85</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GOOGLE*WORKSPACE</t>
+          <t>ZOHO-ZOHO CORP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FINOM-c397c233e5748323</t>
+          <t>FINOM-d0d29a90ec518cd9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -9875,20 +9705,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.99</v>
+        <v>10.28</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GOOGLE*WORKSPACE</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FINOM-a3ba6433c48234cc</t>
+          <t>FINOM-537cc943fa0b335d</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -9905,7 +9735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -9913,12 +9743,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Google Workspace</t>
+          <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FINOM-3bb092b004a4fae3</t>
+          <t>FINOM-c397c233e5748323</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9935,7 +9765,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -9948,7 +9778,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FINOM-3e1804c85955a201</t>
+          <t>FINOM-a3ba6433c48234cc</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9965,20 +9795,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.72</v>
+        <v>8.99</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>Google Workspace</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FINOM-3ceccc883c4b167d</t>
+          <t>FINOM-3bb092b004a4fae3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9995,20 +9825,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.3</v>
+        <v>8.99</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>GOOGLE*WORKSPACE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FINOM-63b607beb1dca136</t>
+          <t>FINOM-3e1804c85955a201</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10025,20 +9855,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.25</v>
+        <v>5.72</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GAMMA.APP</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FINOM-d017c4ac09611a43</t>
+          <t>FINOM-3ceccc883c4b167d</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10055,20 +9885,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.32</v>
+        <v>5.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FINDYLEAD.COM</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FINOM-0934e4ba1f2bf7b5</t>
+          <t>FINOM-63b607beb1dca136</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10080,30 +9910,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Beleg</t>
+          <t>Transaktion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.48</v>
+        <v>5.25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Invoice number CXFCCFMI-0003</t>
+          <t>GAMMA.APP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Invoice-CXFCCFMI-0003.pdf</t>
+          <t>FINOM-d017c4ac09611a43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19% (unterstellt)</t>
         </is>
       </c>
     </row>
@@ -10115,20 +9945,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4.32</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UZR*digistore24.com</t>
+          <t>FINDYLEAD.COM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FINOM-24bba19c4344d8c2</t>
+          <t>FINOM-0934e4ba1f2bf7b5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -10145,23 +9975,83 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Invoice number CXFCCFMI-0003</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Invoice-CXFCCFMI-0003.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Transaktion</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>UZR*digistore24.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FINOM-24bba19c4344d8c2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>19% (unterstellt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Beleg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Digistore24</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Rechnung_TJC9SRX6_73763127-de.pdf</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -11788,7 +11678,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -11835,7 +11725,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -11850,7 +11740,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
@@ -16157,15 +16047,14 @@
       <c r="I84" t="b">
         <v>0</v>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Rechnung_TJC9SRX6_I-74230203-de.pdf</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Vormals faelschlich Funnelcockpit_2.pdf zugeordnet (siehe Korrektur 2026-07-22) - Beleg wurde 08-28 zugewiesen. Echte September-Rechnung noch nicht gefunden.</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>
@@ -18399,10 +18288,19 @@
       <c r="I127" t="b">
         <v>1</v>
       </c>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>(kein Originalbeleg - akzeptiert)</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>AKZEPTIERT_BAGATELLE</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Per Nutzerentscheidung 2026-07-22 akzeptiert: keine Rechnung auffindbar trotz mehrfacher Recherche (Drive komplett, Gmail). Netto geschaetzt mit 19% USt aus Bankbetrag.</t>
         </is>
       </c>
     </row>
@@ -18717,15 +18615,14 @@
       <c r="I133" t="b">
         <v>0</v>
       </c>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>H_34974301.pdf</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>PRUEFFALL</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>Mehrere Beleg-Kandidaten mit passender Rechnungsnummer/Partner+Zeitfenster: H_33541164.pdf (Beleg 6649835b); H_34974301.pdf (Beleg aa369ac3)</t>
+          <t>BELEGT</t>
         </is>
       </c>
     </row>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2319.59</v>
+        <v>2385.11</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>164.36</v>
+        <v>166.55</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>776.14</v>
+        <v>773.95</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2630.41</v>
+        <v>2564.89</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2630.41</v>
+        <v>2564.89</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1315.2</v>
+        <v>1282.44</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2859.06</v>
+        <v>2926.77</v>
       </c>
     </row>
     <row r="15">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -6620,13 +6620,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>167.9</v>
+        <v>172.9</v>
       </c>
       <c r="E6" t="n">
-        <v>181.18</v>
+        <v>186.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-167.9</v>
+        <v>-172.9</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6696,13 +6696,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>151.69</v>
+        <v>156.69</v>
       </c>
       <c r="E8" t="n">
-        <v>164.78</v>
+        <v>169.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-151.69</v>
+        <v>-156.69</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6772,25 +6772,25 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>318.48</v>
+        <v>319.32</v>
       </c>
       <c r="E10" t="n">
-        <v>432.87</v>
+        <v>433.87</v>
       </c>
       <c r="F10" t="n">
-        <v>-318.48</v>
+        <v>-319.32</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>28.67</v>
+        <v>28.83</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-28.67</v>
+        <v>-28.83</v>
       </c>
       <c r="K10" t="n">
         <v>82.98999999999999</v>
@@ -6848,25 +6848,25 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>719.08</v>
+        <v>720.24</v>
       </c>
       <c r="E12" t="n">
-        <v>749.38</v>
+        <v>750.76</v>
       </c>
       <c r="F12" t="n">
-        <v>-294.08</v>
+        <v>-295.24</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
       </c>
       <c r="H12" t="n">
-        <v>27.95</v>
+        <v>28.17</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>52.8</v>
+        <v>52.58</v>
       </c>
       <c r="K12" t="n">
         <v>10.28</v>
@@ -6886,31 +6886,31 @@
         <v>4760</v>
       </c>
       <c r="D13" t="n">
-        <v>153.71</v>
+        <v>207.23</v>
       </c>
       <c r="E13" t="n">
-        <v>162.25</v>
+        <v>217.58</v>
       </c>
       <c r="F13" t="n">
-        <v>3846.29</v>
+        <v>3792.77</v>
       </c>
       <c r="G13" t="n">
         <v>760</v>
       </c>
       <c r="H13" t="n">
-        <v>6.83</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>753.17</v>
+        <v>751.36</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -6926,31 +6926,31 @@
         <v>5890.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2319.59</v>
+        <v>2385.11</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2859.06</v>
+        <v>2926.77</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2630.41</v>
+        <v>2564.89</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>164.36</v>
+        <v>166.55</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>776.14</v>
+        <v>773.95</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>391.72</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2986.24</v>
+        <v>2976.24</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1963.76</v>
+        <v>1973.76</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1963.76</v>
+        <v>1973.76</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>981.88</v>
+        <v>986.88</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3257.75</v>
+        <v>3247.75</v>
       </c>
     </row>
     <row r="15">
@@ -703,7 +703,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>BAGATELLE_IGNORIERT</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>169.78</v>
+        <v>164.78</v>
       </c>
     </row>
     <row r="14">
@@ -6589,13 +6589,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>172.9</v>
+        <v>167.9</v>
       </c>
       <c r="E6" t="n">
-        <v>186.18</v>
+        <v>181.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-172.9</v>
+        <v>-167.9</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6665,13 +6665,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>156.69</v>
+        <v>151.69</v>
       </c>
       <c r="E8" t="n">
-        <v>169.78</v>
+        <v>164.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-156.69</v>
+        <v>-151.69</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6895,13 +6895,13 @@
         <v>5890.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2986.24</v>
+        <v>2976.24</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3257.75</v>
+        <v>3247.75</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1963.76</v>
+        <v>1973.76</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
@@ -10002,7 +10002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -10160,39 +10160,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PNL Fintech B.V.</t>
+          <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>29.76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unregelmaessig/monatlich (wenige Datenpunkte)</t>
+          <t>monatlich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5, 7</t>
+          <t>1, 2, 3, 5, 7, 9, 10, 11, 12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4, 6, 8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>327.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRIATHLON TRANSFER GMBH</t>
+          <t>UZR*digistore24.com</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.76</v>
+        <v>55.92</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -10201,43 +10201,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1, 2, 3, 5, 7, 9, 10, 11, 12</t>
+          <t>8, 9, 10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4, 6, 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>327.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>UZR*digistore24.com</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>monatlich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8, 9, 10</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
         <v>167.79</v>
       </c>
     </row>
@@ -11699,7 +11671,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -13529,7 +13501,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>BAGATELLE_IGNORIERT</t>
         </is>
       </c>
       <c r="I36" t="b">
@@ -14403,7 +14375,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>BAGATELLE_IGNORIERT</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -20463,7 +20435,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -20915,7 +20887,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>BAGATELLE_IGNORIERT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20992,7 +20964,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>186.18</v>
+        <v>181.18</v>
       </c>
     </row>
     <row r="16">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2976.24</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219.39</v>
+        <v>215.98</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>721.11</v>
+        <v>724.52</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1973.76</v>
+        <v>1991.68</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1973.76</v>
+        <v>1991.68</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>986.88</v>
+        <v>995.84</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3247.75</v>
+        <v>3203.29</v>
       </c>
     </row>
     <row r="15">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3399,7 +3399,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>KEIN_BELEG_AUSGESCHLOSSEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>759.75</v>
+        <v>749.47</v>
       </c>
     </row>
     <row r="19">
@@ -4062,7 +4062,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>KEIN_BELEG_AUSGESCHLOSSEN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4991.82</v>
+        <v>4970.49</v>
       </c>
     </row>
     <row r="33">
@@ -6554,7 +6554,7 @@
         <v>87.34999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>103.98</v>
+        <v>91.13</v>
       </c>
       <c r="F5" t="n">
         <v>-87.34999999999999</v>
@@ -6572,7 +6572,7 @@
         <v>-3.78</v>
       </c>
       <c r="K5" t="n">
-        <v>12.85</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>720.24</v>
       </c>
       <c r="E12" t="n">
-        <v>750.76</v>
+        <v>740.48</v>
       </c>
       <c r="F12" t="n">
         <v>-295.24</v>
@@ -6838,7 +6838,7 @@
         <v>52.58</v>
       </c>
       <c r="K12" t="n">
-        <v>10.28</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -6855,25 +6855,25 @@
         <v>4760</v>
       </c>
       <c r="D13" t="n">
-        <v>207.23</v>
+        <v>189.31</v>
       </c>
       <c r="E13" t="n">
-        <v>217.58</v>
+        <v>196.25</v>
       </c>
       <c r="F13" t="n">
-        <v>3792.77</v>
+        <v>3810.69</v>
       </c>
       <c r="G13" t="n">
         <v>760</v>
       </c>
       <c r="H13" t="n">
-        <v>8.640000000000001</v>
+        <v>5.23</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>751.36</v>
+        <v>754.77</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -6895,28 +6895,28 @@
         <v>5890.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2976.24</v>
+        <v>2958.32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3247.75</v>
+        <v>3203.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1973.76</v>
+        <v>1991.68</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>219.39</v>
+        <v>215.98</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>721.11</v>
+        <v>724.52</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>23.13</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>32</v>
@@ -11671,7 +11671,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>KEIN_BELEG_AUSGESCHLOSSEN</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>KEIN_BELEG_AUSGESCHLOSSEN</t>
         </is>
       </c>
       <c r="I106" t="b">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>KEIN_BELEG_AUSGESCHLOSSEN</t>
         </is>
       </c>
       <c r="I130" t="b">
@@ -19930,7 +19930,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GESCHAEFTLICH</t>
+          <t>KEIN_BELEG_AUSGESCHLOSSEN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -20393,7 +20393,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>103.98</v>
+        <v>91.13</v>
       </c>
     </row>
     <row r="15">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4950</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>940.5</v>
+        <v>921.5</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2958.32</v>
+        <v>3058.32</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>215.98</v>
+        <v>234.98</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>724.52</v>
+        <v>686.52</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1991.68</v>
+        <v>1791.68</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1991.68</v>
+        <v>1791.68</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>995.84</v>
+        <v>895.84</v>
       </c>
     </row>
     <row r="11">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5890.5</v>
+        <v>5771.5</v>
       </c>
     </row>
     <row r="14">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3203.29</v>
+        <v>3322.29</v>
       </c>
     </row>
     <row r="15">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>212.27</v>
+        <v>93.27</v>
       </c>
     </row>
     <row r="22">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>699.8200000000001</v>
+        <v>818.8200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -5345,7 +5345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5469,20 +5469,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>119</v>
+        <v>275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Joel Wagner</t>
+          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RE250005 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
+          <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5492,103 +5492,108 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rechnung Joel Wagner.pdf</t>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RE250005</t>
+          <t>RE250006</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Anzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>275</v>
+        <v>155.1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JA</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rechnung Vapi Martin Veser.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>RE250006</t>
+          <t>NEIN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELEGT</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Anzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
+          <t>BELEG_FEHLT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>155.1</v>
+        <v>230.75</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NEIN</t>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RE250006</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Restzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>230.75</v>
+        <v>505.75</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5597,7 +5602,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5607,42 +5612,37 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rechnung Vapi Martin Veser.pdf</t>
+          <t>Rechnung RE250007.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RE250006</t>
+          <t>RE250007</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>BELEGT</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Restzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>505.75</v>
+        <v>4760</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
+          <t>Joel Wagner</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rechnung RE250007.pdf</t>
+          <t>Rechnung RE250009.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RE250007</t>
+          <t>RE250009</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5669,7 +5669,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5677,65 +5677,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Joel Wagner</t>
+          <t>Benito Ferrise</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
+          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JA</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Rechnung RE250009.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>RE250009</t>
+          <t>NEIN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BELEGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4760</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Benito Ferrise</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NEIN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
           <t>PRUEFFALL</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 4760.0 am 2025-12-31 bei mehreren Buchungen: Benito Ferrise (EINGANG), Benito Ferrise (AUSGANG)</t>
         </is>
@@ -6697,31 +6657,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>598.22</v>
+        <v>698.22</v>
       </c>
       <c r="E9" t="n">
-        <v>689.2</v>
+        <v>808.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-498.22</v>
+        <v>-698.22</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>92.53</v>
+        <v>111.53</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-73.53</v>
+        <v>-111.53</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -6889,31 +6849,31 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4950</v>
+        <v>4850</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5890.5</v>
+        <v>5771.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2958.32</v>
+        <v>3058.32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3203.29</v>
+        <v>3322.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1991.68</v>
+        <v>1791.68</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>940.5</v>
+        <v>921.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>215.98</v>
+        <v>234.98</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>724.52</v>
+        <v>686.52</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -15203,7 +15163,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>UMSATZ (Geld rein)</t>
+          <t>AUSGABE (Geld raus)</t>
         </is>
       </c>
       <c r="E70" t="n">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4850</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>921.5</v>
+        <v>940.5</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3058.32</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>234.98</v>
+        <v>215.98</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>686.52</v>
+        <v>724.52</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1791.68</v>
+        <v>1991.68</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1791.68</v>
+        <v>1991.68</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>895.84</v>
+        <v>995.84</v>
       </c>
     </row>
     <row r="11">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5771.5</v>
+        <v>5890.5</v>
       </c>
     </row>
     <row r="14">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3322.29</v>
+        <v>3203.29</v>
       </c>
     </row>
     <row r="15">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>93.27</v>
+        <v>212.27</v>
       </c>
     </row>
     <row r="22">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>818.8200000000001</v>
+        <v>699.8200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -5345,7 +5345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5469,20 +5469,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>275</v>
+        <v>119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
+          <t>Joel Wagner</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>RE250005 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5492,108 +5492,103 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rechnung Vapi Martin Veser.pdf</t>
+          <t>Rechnung Joel Wagner.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RE250006</t>
+          <t>RE250005</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>BELEGT</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Anzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>155.1</v>
+        <v>275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finanzamt Saarlouis -Finanzkasse-</t>
+          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
+          <t>WebWokr Angebot AG0011 AZ | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NEIN</t>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RE250006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELEG_FEHLT</t>
+          <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Anzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>230.75</v>
+        <v>155.1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
+          <t>Finanzamt Saarlouis -Finanzkasse-</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>ERSTATT.040/163/12016 UMS.ST 3VJ.25 | 155,10 EUR | IBAN: DE50590000000059301502 | BIC: MARKDEF1590</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JA</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rechnung Vapi Martin Veser.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>RE250006</t>
+          <t>NEIN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BELEGT</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Restzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
+          <t>BELEG_FEHLT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>505.75</v>
+        <v>230.75</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5602,7 +5597,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
+          <t>Rechnung RE250006 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5612,37 +5607,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rechnung RE250007.pdf</t>
+          <t>Rechnung Vapi Martin Veser.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RE250007</t>
+          <t>RE250006</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>BELEGT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Restzahlung auf Rechnung RE250006 (23.10.2025, Gesamtbetrag 505,75 EUR = 275,00 AZ + 230,75 Rest). Aus Drive nachgeladen 2026-07-22.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4760</v>
+        <v>505.75</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Joel Wagner</t>
+          <t>Martin Veser UG (haftungsbeschr?nkt)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
+          <t>Rechnung RE250007 | IBAN: DE68100101231039496522 | BIC: QNTODEB2XXX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rechnung RE250009.pdf</t>
+          <t>Rechnung RE250007.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RE250009</t>
+          <t>RE250007</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5669,7 +5669,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5677,25 +5677,65 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Joel Wagner</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RE250009 | IBAN: DE90590501010067196121 | BIC: SAKSDE55XXX</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rechnung RE250009.pdf</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RE250009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>BELEGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4760</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Benito Ferrise</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Retainer Q1 2026 | IBAN: DE66590501010067216341 | BIC: SAKSDE55XXX</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>NEIN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>PRUEFFALL</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Duplikat-/Rundlauf-Verdacht: gleicher Betrag 4760.0 am 2025-12-31 bei mehreren Buchungen: Benito Ferrise (EINGANG), Benito Ferrise (AUSGANG)</t>
         </is>
@@ -6657,31 +6697,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="D9" t="n">
-        <v>698.22</v>
+        <v>598.22</v>
       </c>
       <c r="E9" t="n">
-        <v>808.2</v>
+        <v>689.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-698.22</v>
+        <v>-498.22</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>111.53</v>
+        <v>92.53</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-111.53</v>
+        <v>-73.53</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -6849,31 +6889,31 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4850</v>
+        <v>4950</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5771.5</v>
+        <v>5890.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3058.32</v>
+        <v>2958.32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3322.29</v>
+        <v>3203.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1791.68</v>
+        <v>1991.68</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>921.5</v>
+        <v>940.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>234.98</v>
+        <v>215.98</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>686.52</v>
+        <v>724.52</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -15163,7 +15203,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AUSGABE (Geld raus)</t>
+          <t>UMSATZ (Geld rein)</t>
         </is>
       </c>
       <c r="E70" t="n">

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2958.32</v>
+        <v>2976.79</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>215.98</v>
+        <v>249.76</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>724.52</v>
+        <v>690.74</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1991.68</v>
+        <v>1973.21</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1991.68</v>
+        <v>1973.21</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>995.84</v>
+        <v>986.61</v>
       </c>
     </row>
     <row r="11">
@@ -6449,13 +6449,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89</v>
+        <v>6.64</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.89</v>
+        <v>-6.64</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -6487,13 +6487,13 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.78</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.78</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -6525,13 +6525,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.78</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.78</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.78</v>
+        <v>13.28</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.78</v>
+        <v>-13.28</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -6677,13 +6677,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8.34</v>
+        <v>13.09</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-8.34</v>
+        <v>-13.09</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>47.83</v>
+        <v>52.58</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-47.83</v>
+        <v>-52.58</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -6791,13 +6791,13 @@
         <v>80.75</v>
       </c>
       <c r="H11" t="n">
-        <v>13.09</v>
+        <v>22.59</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>67.66</v>
+        <v>58.16</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -6817,25 +6817,25 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>720.24</v>
+        <v>738.71</v>
       </c>
       <c r="E12" t="n">
         <v>740.48</v>
       </c>
       <c r="F12" t="n">
-        <v>-295.24</v>
+        <v>-313.71</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
       </c>
       <c r="H12" t="n">
-        <v>28.17</v>
+        <v>14.45</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>52.58</v>
+        <v>66.3</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -6867,13 +6867,13 @@
         <v>760</v>
       </c>
       <c r="H13" t="n">
-        <v>5.23</v>
+        <v>9.98</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>754.77</v>
+        <v>750.02</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -6895,25 +6895,25 @@
         <v>5890.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2958.32</v>
+        <v>2976.79</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>3203.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1991.68</v>
+        <v>1973.21</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>215.98</v>
+        <v>249.76</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>724.52</v>
+        <v>690.74</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4950</v>
+        <v>5223.96</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>986.61</v>
+        <v>1123.59</v>
       </c>
     </row>
     <row r="11">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5890.5</v>
+        <v>6164.46</v>
       </c>
     </row>
     <row r="14">
@@ -6659,10 +6659,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
       <c r="D8" t="n">
         <v>151.69</v>
@@ -6671,7 +6671,7 @@
         <v>164.78</v>
       </c>
       <c r="F8" t="n">
-        <v>-151.69</v>
+        <v>-126.1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>193.27</v>
       </c>
       <c r="C9" t="n">
-        <v>119</v>
+        <v>212.27</v>
       </c>
       <c r="D9" t="n">
         <v>598.22</v>
@@ -6709,7 +6709,7 @@
         <v>689.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-498.22</v>
+        <v>-404.95</v>
       </c>
       <c r="G9" t="n">
         <v>19</v>
@@ -6773,10 +6773,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>425</v>
+        <v>580.1</v>
       </c>
       <c r="C11" t="n">
-        <v>505.75</v>
+        <v>660.85</v>
       </c>
       <c r="D11" t="n">
         <v>237.17</v>
@@ -6785,7 +6785,7 @@
         <v>259.76</v>
       </c>
       <c r="F11" t="n">
-        <v>187.83</v>
+        <v>342.93</v>
       </c>
       <c r="G11" t="n">
         <v>80.75</v>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4950</v>
+        <v>5223.96</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5890.5</v>
+        <v>6164.46</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2976.79</v>
@@ -6901,7 +6901,7 @@
         <v>3203.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1973.21</v>
+        <v>2247.17</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>

--- a/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
+++ b/Finanzen/Belegauswertung_2025/out/ergebnis_2025.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2976.79</v>
+        <v>2958.32</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="9">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1123.59</v>
+        <v>1132.82</v>
       </c>
     </row>
     <row r="11">
@@ -6817,13 +6817,13 @@
         <v>505.75</v>
       </c>
       <c r="D12" t="n">
-        <v>738.71</v>
+        <v>720.24</v>
       </c>
       <c r="E12" t="n">
         <v>740.48</v>
       </c>
       <c r="F12" t="n">
-        <v>-313.71</v>
+        <v>-295.24</v>
       </c>
       <c r="G12" t="n">
         <v>80.75</v>
@@ -6895,13 +6895,13 @@
         <v>6164.46</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2976.79</v>
+        <v>2958.32</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>3203.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2247.17</v>
+        <v>2265.64</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>940.5</v>
